--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260617_215156.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260617_215156.xlsx
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6982,7 +6982,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260617_215156.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260617_215156.xlsx
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6982,7 +6982,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
